--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="242">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -735,6 +735,12 @@
   <si>
     <t>['2']</t>
   </si>
+  <si>
+    <t>['43', '90']</t>
+  </si>
+  <si>
+    <t>['11', '28', '49', '54', '89', '90+2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1095,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2459,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ7">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3283,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.09</v>
@@ -3698,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR13">
         <v>2.12</v>
@@ -4313,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ16">
         <v>0.7</v>
@@ -4519,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>1.09</v>
@@ -6373,7 +6379,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ26">
         <v>2.3</v>
@@ -6994,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR29">
         <v>1.93</v>
@@ -7612,7 +7618,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ32">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR32">
         <v>2.16</v>
@@ -7815,7 +7821,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ33">
         <v>1.45</v>
@@ -8021,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>0.7</v>
@@ -8227,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ35">
         <v>0.27</v>
@@ -8642,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR37">
         <v>1.1</v>
@@ -9463,7 +9469,7 @@
         <v>1.33</v>
       </c>
       <c r="AP41">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ41">
         <v>0.82</v>
@@ -9875,7 +9881,7 @@
         <v>1.75</v>
       </c>
       <c r="AP43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>1.9</v>
@@ -10290,7 +10296,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ45">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR45">
         <v>1.74</v>
@@ -11114,7 +11120,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ49">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR49">
         <v>2.19</v>
@@ -11523,7 +11529,7 @@
         <v>2.4</v>
       </c>
       <c r="AP51">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>1.45</v>
@@ -11732,7 +11738,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ52">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR52">
         <v>1.62</v>
@@ -13789,7 +13795,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ62">
         <v>1.9</v>
@@ -13998,7 +14004,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14204,7 +14210,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR64">
         <v>3.13</v>
@@ -14613,7 +14619,7 @@
         <v>2.6</v>
       </c>
       <c r="AP66">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>2.3</v>
@@ -14822,7 +14828,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ67">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>1.7</v>
@@ -16673,7 +16679,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ76">
         <v>1.09</v>
@@ -17500,7 +17506,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ80">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR80">
         <v>1.28</v>
@@ -17703,7 +17709,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>2.1</v>
@@ -17912,7 +17918,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR82">
         <v>1.39</v>
@@ -19557,7 +19563,7 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
         <v>0.82</v>
@@ -19972,7 +19978,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ92">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -21414,7 +21420,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ99">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
         <v>1.69</v>
@@ -22444,7 +22450,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ104">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR104">
         <v>1.45</v>
@@ -22853,7 +22859,7 @@
         <v>2.25</v>
       </c>
       <c r="AP106">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ106">
         <v>2.1</v>
@@ -23677,7 +23683,7 @@
         <v>1.22</v>
       </c>
       <c r="AP110">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ110">
         <v>1.09</v>
@@ -23883,10 +23889,10 @@
         <v>2</v>
       </c>
       <c r="AP111">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR111">
         <v>0.97</v>
@@ -24092,7 +24098,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ112">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR112">
         <v>2.55</v>
@@ -24504,7 +24510,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ114">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR114">
         <v>1.45</v>
@@ -24707,7 +24713,7 @@
         <v>1.22</v>
       </c>
       <c r="AP115">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -26564,7 +26570,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ124">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR124">
         <v>1.41</v>
@@ -27052,6 +27058,418 @@
       </c>
       <c r="BP126">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7727618</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45668.40625</v>
+      </c>
+      <c r="F127">
+        <v>21</v>
+      </c>
+      <c r="G127" t="s">
+        <v>75</v>
+      </c>
+      <c r="H127" t="s">
+        <v>79</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>2</v>
+      </c>
+      <c r="N127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>85</v>
+      </c>
+      <c r="P127" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q127">
+        <v>2.3</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>4.75</v>
+      </c>
+      <c r="T127">
+        <v>1.36</v>
+      </c>
+      <c r="U127">
+        <v>3</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>6.5</v>
+      </c>
+      <c r="Y127">
+        <v>1.1</v>
+      </c>
+      <c r="Z127">
+        <v>1.73</v>
+      </c>
+      <c r="AA127">
+        <v>3.8</v>
+      </c>
+      <c r="AB127">
+        <v>4.2</v>
+      </c>
+      <c r="AC127">
+        <v>1.04</v>
+      </c>
+      <c r="AD127">
+        <v>11</v>
+      </c>
+      <c r="AE127">
+        <v>1.27</v>
+      </c>
+      <c r="AF127">
+        <v>3.55</v>
+      </c>
+      <c r="AG127">
+        <v>1.6</v>
+      </c>
+      <c r="AH127">
+        <v>2.08</v>
+      </c>
+      <c r="AI127">
+        <v>1.83</v>
+      </c>
+      <c r="AJ127">
+        <v>1.83</v>
+      </c>
+      <c r="AK127">
+        <v>1.21</v>
+      </c>
+      <c r="AL127">
+        <v>1.24</v>
+      </c>
+      <c r="AM127">
+        <v>2.05</v>
+      </c>
+      <c r="AN127">
+        <v>1.7</v>
+      </c>
+      <c r="AO127">
+        <v>1.8</v>
+      </c>
+      <c r="AP127">
+        <v>1.55</v>
+      </c>
+      <c r="AQ127">
+        <v>1.91</v>
+      </c>
+      <c r="AR127">
+        <v>1.34</v>
+      </c>
+      <c r="AS127">
+        <v>1.38</v>
+      </c>
+      <c r="AT127">
+        <v>2.72</v>
+      </c>
+      <c r="AU127">
+        <v>6</v>
+      </c>
+      <c r="AV127">
+        <v>9</v>
+      </c>
+      <c r="AW127">
+        <v>8</v>
+      </c>
+      <c r="AX127">
+        <v>9</v>
+      </c>
+      <c r="AY127">
+        <v>14</v>
+      </c>
+      <c r="AZ127">
+        <v>18</v>
+      </c>
+      <c r="BA127">
+        <v>0</v>
+      </c>
+      <c r="BB127">
+        <v>7</v>
+      </c>
+      <c r="BC127">
+        <v>7</v>
+      </c>
+      <c r="BD127">
+        <v>1.39</v>
+      </c>
+      <c r="BE127">
+        <v>7.3</v>
+      </c>
+      <c r="BF127">
+        <v>3.84</v>
+      </c>
+      <c r="BG127">
+        <v>1.19</v>
+      </c>
+      <c r="BH127">
+        <v>3.82</v>
+      </c>
+      <c r="BI127">
+        <v>1.38</v>
+      </c>
+      <c r="BJ127">
+        <v>2.62</v>
+      </c>
+      <c r="BK127">
+        <v>1.7</v>
+      </c>
+      <c r="BL127">
+        <v>2.05</v>
+      </c>
+      <c r="BM127">
+        <v>2.1</v>
+      </c>
+      <c r="BN127">
+        <v>1.59</v>
+      </c>
+      <c r="BO127">
+        <v>2.78</v>
+      </c>
+      <c r="BP127">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7727624</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45668.40625</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" t="s">
+        <v>74</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>3</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>6</v>
+      </c>
+      <c r="N128">
+        <v>7</v>
+      </c>
+      <c r="O128" t="s">
+        <v>138</v>
+      </c>
+      <c r="P128" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q128">
+        <v>2.75</v>
+      </c>
+      <c r="R128">
+        <v>2.3</v>
+      </c>
+      <c r="S128">
+        <v>3.1</v>
+      </c>
+      <c r="T128">
+        <v>1.29</v>
+      </c>
+      <c r="U128">
+        <v>3.5</v>
+      </c>
+      <c r="V128">
+        <v>2.38</v>
+      </c>
+      <c r="W128">
+        <v>1.53</v>
+      </c>
+      <c r="X128">
+        <v>5</v>
+      </c>
+      <c r="Y128">
+        <v>1.14</v>
+      </c>
+      <c r="Z128">
+        <v>2.25</v>
+      </c>
+      <c r="AA128">
+        <v>3.25</v>
+      </c>
+      <c r="AB128">
+        <v>2.75</v>
+      </c>
+      <c r="AC128">
+        <v>1</v>
+      </c>
+      <c r="AD128">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE128">
+        <v>1.15</v>
+      </c>
+      <c r="AF128">
+        <v>4.25</v>
+      </c>
+      <c r="AG128">
+        <v>1.66</v>
+      </c>
+      <c r="AH128">
+        <v>2.05</v>
+      </c>
+      <c r="AI128">
+        <v>1.5</v>
+      </c>
+      <c r="AJ128">
+        <v>2.5</v>
+      </c>
+      <c r="AK128">
+        <v>1.36</v>
+      </c>
+      <c r="AL128">
+        <v>1.28</v>
+      </c>
+      <c r="AM128">
+        <v>1.51</v>
+      </c>
+      <c r="AN128">
+        <v>1.1</v>
+      </c>
+      <c r="AO128">
+        <v>0.6</v>
+      </c>
+      <c r="AP128">
+        <v>1</v>
+      </c>
+      <c r="AQ128">
+        <v>0.82</v>
+      </c>
+      <c r="AR128">
+        <v>1.06</v>
+      </c>
+      <c r="AS128">
+        <v>1.31</v>
+      </c>
+      <c r="AT128">
+        <v>2.37</v>
+      </c>
+      <c r="AU128">
+        <v>5</v>
+      </c>
+      <c r="AV128">
+        <v>10</v>
+      </c>
+      <c r="AW128">
+        <v>6</v>
+      </c>
+      <c r="AX128">
+        <v>7</v>
+      </c>
+      <c r="AY128">
+        <v>11</v>
+      </c>
+      <c r="AZ128">
+        <v>17</v>
+      </c>
+      <c r="BA128">
+        <v>5</v>
+      </c>
+      <c r="BB128">
+        <v>4</v>
+      </c>
+      <c r="BC128">
+        <v>9</v>
+      </c>
+      <c r="BD128">
+        <v>0</v>
+      </c>
+      <c r="BE128">
+        <v>0</v>
+      </c>
+      <c r="BF128">
+        <v>0</v>
+      </c>
+      <c r="BG128">
+        <v>0</v>
+      </c>
+      <c r="BH128">
+        <v>0</v>
+      </c>
+      <c r="BI128">
+        <v>0</v>
+      </c>
+      <c r="BJ128">
+        <v>0</v>
+      </c>
+      <c r="BK128">
+        <v>0</v>
+      </c>
+      <c r="BL128">
+        <v>0</v>
+      </c>
+      <c r="BM128">
+        <v>0</v>
+      </c>
+      <c r="BN128">
+        <v>0</v>
+      </c>
+      <c r="BO128">
+        <v>0</v>
+      </c>
+      <c r="BP128">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,15 @@
     <t>['63', '90+9']</t>
   </si>
   <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['47', '80', '84']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -740,6 +749,12 @@
   </si>
   <si>
     <t>['11', '28', '49', '54', '89', '90+2']</t>
+  </si>
+  <si>
+    <t>['5', '47']</t>
+  </si>
+  <si>
+    <t>['39', '89']</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1357,7 +1372,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1435,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ2">
         <v>0.27</v>
@@ -1563,7 +1578,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1641,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3">
         <v>1.2</v>
@@ -1769,7 +1784,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2056,7 +2071,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2181,7 +2196,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2262,7 +2277,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ6">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2671,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8">
         <v>1.09</v>
@@ -2799,7 +2814,7 @@
         <v>88</v>
       </c>
       <c r="P9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q9">
         <v>11</v>
@@ -2880,7 +2895,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR9">
         <v>1.59</v>
@@ -3211,7 +3226,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3417,7 +3432,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3495,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3623,7 +3638,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q13">
         <v>2.63</v>
@@ -3701,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ13">
         <v>1.91</v>
@@ -3829,7 +3844,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4116,7 +4131,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4322,7 +4337,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ16">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR16">
         <v>1.91</v>
@@ -4731,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18">
         <v>1.2</v>
@@ -4937,10 +4952,10 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ19">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR19">
         <v>1.34</v>
@@ -5065,7 +5080,7 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>4.75</v>
@@ -5477,7 +5492,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5555,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ22">
         <v>0.82</v>
@@ -5889,7 +5904,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5967,7 +5982,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24">
         <v>1.45</v>
@@ -6095,7 +6110,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>5.5</v>
@@ -6301,7 +6316,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -6382,7 +6397,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ26">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR26">
         <v>1.81</v>
@@ -6507,7 +6522,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q27">
         <v>2.38</v>
@@ -6585,10 +6600,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ27">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR27">
         <v>1.77</v>
@@ -6997,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ29">
         <v>0.82</v>
@@ -7125,7 +7140,7 @@
         <v>85</v>
       </c>
       <c r="P30" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q30">
         <v>13</v>
@@ -7206,7 +7221,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ30">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR30">
         <v>1.46</v>
@@ -7331,7 +7346,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>1.83</v>
@@ -7949,7 +7964,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8030,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
         <v>0.86</v>
@@ -8439,7 +8454,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ36">
         <v>1.45</v>
@@ -8567,7 +8582,7 @@
         <v>107</v>
       </c>
       <c r="P37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q37">
         <v>1.83</v>
@@ -8645,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ37">
         <v>0.82</v>
@@ -8854,7 +8869,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ38">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR38">
         <v>1.69</v>
@@ -9266,7 +9281,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9391,7 +9406,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9597,7 +9612,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>7</v>
@@ -9678,7 +9693,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ42">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR42">
         <v>2.47</v>
@@ -9803,7 +9818,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9884,7 +9899,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR43">
         <v>0.99</v>
@@ -10087,7 +10102,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ44">
         <v>1.09</v>
@@ -10293,7 +10308,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ45">
         <v>1.91</v>
@@ -10421,7 +10436,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10502,7 +10517,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ46">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR46">
         <v>0.8100000000000001</v>
@@ -10627,7 +10642,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10833,7 +10848,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11245,7 +11260,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11451,7 +11466,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11657,7 +11672,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12147,7 +12162,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54">
         <v>0.27</v>
@@ -12275,7 +12290,7 @@
         <v>114</v>
       </c>
       <c r="P55" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12353,10 +12368,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ55">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR55">
         <v>1.83</v>
@@ -12481,7 +12496,7 @@
         <v>85</v>
       </c>
       <c r="P56" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q56">
         <v>6.5</v>
@@ -12562,7 +12577,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ56">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR56">
         <v>1.7</v>
@@ -12687,7 +12702,7 @@
         <v>122</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>7</v>
@@ -12971,7 +12986,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13305,7 +13320,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13383,10 +13398,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ60">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR60">
         <v>1.7</v>
@@ -13717,7 +13732,7 @@
         <v>85</v>
       </c>
       <c r="P62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13798,7 +13813,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ62">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -13923,7 +13938,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14001,7 +14016,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ63">
         <v>1.91</v>
@@ -14129,7 +14144,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14541,7 +14556,7 @@
         <v>85</v>
       </c>
       <c r="P66" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q66">
         <v>9</v>
@@ -14622,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR66">
         <v>0.96</v>
@@ -14825,7 +14840,7 @@
         <v>0.75</v>
       </c>
       <c r="AP67">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ67">
         <v>0.82</v>
@@ -14953,7 +14968,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15031,7 +15046,7 @@
         <v>1.2</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ68">
         <v>0.82</v>
@@ -15159,7 +15174,7 @@
         <v>130</v>
       </c>
       <c r="P69" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15652,7 +15667,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ71">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR71">
         <v>2.71</v>
@@ -15777,7 +15792,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q72">
         <v>2.88</v>
@@ -15855,7 +15870,7 @@
         <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ72">
         <v>1.09</v>
@@ -16061,10 +16076,10 @@
         <v>2.67</v>
       </c>
       <c r="AP73">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ73">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR73">
         <v>1.22</v>
@@ -16189,7 +16204,7 @@
         <v>135</v>
       </c>
       <c r="P74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q74">
         <v>1.73</v>
@@ -16267,7 +16282,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ74">
         <v>0.27</v>
@@ -16395,7 +16410,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q75">
         <v>7</v>
@@ -16476,7 +16491,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ75">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR75">
         <v>1.05</v>
@@ -16807,7 +16822,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16885,7 +16900,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ77">
         <v>0.82</v>
@@ -17013,7 +17028,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>2.75</v>
@@ -17219,7 +17234,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q79">
         <v>3.1</v>
@@ -17631,7 +17646,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17712,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -17837,7 +17852,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18043,7 +18058,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18124,7 +18139,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18249,7 +18264,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18327,10 +18342,10 @@
         <v>2.5</v>
       </c>
       <c r="AP84">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -18533,7 +18548,7 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ85">
         <v>1.2</v>
@@ -18742,7 +18757,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ86">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR86">
         <v>1.32</v>
@@ -19073,7 +19088,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q88">
         <v>4.75</v>
@@ -19151,10 +19166,10 @@
         <v>2.43</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR88">
         <v>1.4</v>
@@ -19485,7 +19500,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19691,7 +19706,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19769,7 +19784,7 @@
         <v>1.29</v>
       </c>
       <c r="AP91">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91">
         <v>1.09</v>
@@ -20184,7 +20199,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR93">
         <v>1.97</v>
@@ -20309,7 +20324,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20387,7 +20402,7 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ94">
         <v>1.2</v>
@@ -20596,7 +20611,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ95">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR95">
         <v>2.71</v>
@@ -20721,7 +20736,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20802,7 +20817,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ96">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -20927,7 +20942,7 @@
         <v>154</v>
       </c>
       <c r="P97" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q97">
         <v>1.73</v>
@@ -21008,7 +21023,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ97">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR97">
         <v>2.55</v>
@@ -21211,7 +21226,7 @@
         <v>0.38</v>
       </c>
       <c r="AP98">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ98">
         <v>0.27</v>
@@ -21751,7 +21766,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21829,7 +21844,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ101">
         <v>1.09</v>
@@ -21957,7 +21972,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22244,7 +22259,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ103">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR103">
         <v>1.93</v>
@@ -22369,7 +22384,7 @@
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q104">
         <v>2.88</v>
@@ -22862,7 +22877,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ106">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR106">
         <v>1.31</v>
@@ -22987,7 +23002,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23065,7 +23080,7 @@
         <v>1.67</v>
       </c>
       <c r="AP107">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ107">
         <v>1.45</v>
@@ -23193,7 +23208,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23271,7 +23286,7 @@
         <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108">
         <v>1.09</v>
@@ -23477,10 +23492,10 @@
         <v>0.88</v>
       </c>
       <c r="AP109">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ109">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR109">
         <v>1.26</v>
@@ -23605,7 +23620,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24017,7 +24032,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24223,7 +24238,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24301,10 +24316,10 @@
         <v>2.22</v>
       </c>
       <c r="AP113">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ113">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24429,7 +24444,7 @@
         <v>99</v>
       </c>
       <c r="P114" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24507,7 +24522,7 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114">
         <v>0.82</v>
@@ -24841,7 +24856,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q116">
         <v>6</v>
@@ -24919,10 +24934,10 @@
         <v>2</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ116">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR116">
         <v>1.4</v>
@@ -25047,7 +25062,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25128,7 +25143,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR117">
         <v>1.49</v>
@@ -25253,7 +25268,7 @@
         <v>85</v>
       </c>
       <c r="P118" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q118">
         <v>3.75</v>
@@ -25331,10 +25346,10 @@
         <v>1.78</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ118">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR118">
         <v>1.68</v>
@@ -25871,7 +25886,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26901,7 +26916,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q126">
         <v>1.44</v>
@@ -27107,7 +27122,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27313,7 +27328,7 @@
         <v>138</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27470,6 +27485,830 @@
       </c>
       <c r="BP128">
         <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7727634</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>71</v>
+      </c>
+      <c r="H129" t="s">
+        <v>80</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>2</v>
+      </c>
+      <c r="O129" t="s">
+        <v>176</v>
+      </c>
+      <c r="P129" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q129">
+        <v>4</v>
+      </c>
+      <c r="R129">
+        <v>2.25</v>
+      </c>
+      <c r="S129">
+        <v>2.4</v>
+      </c>
+      <c r="T129">
+        <v>1.33</v>
+      </c>
+      <c r="U129">
+        <v>3.25</v>
+      </c>
+      <c r="V129">
+        <v>2.63</v>
+      </c>
+      <c r="W129">
+        <v>1.44</v>
+      </c>
+      <c r="X129">
+        <v>6</v>
+      </c>
+      <c r="Y129">
+        <v>1.11</v>
+      </c>
+      <c r="Z129">
+        <v>3.3</v>
+      </c>
+      <c r="AA129">
+        <v>3.6</v>
+      </c>
+      <c r="AB129">
+        <v>1.83</v>
+      </c>
+      <c r="AC129">
+        <v>1.01</v>
+      </c>
+      <c r="AD129">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE129">
+        <v>1.2</v>
+      </c>
+      <c r="AF129">
+        <v>3.68</v>
+      </c>
+      <c r="AG129">
+        <v>1.8</v>
+      </c>
+      <c r="AH129">
+        <v>1.88</v>
+      </c>
+      <c r="AI129">
+        <v>1.67</v>
+      </c>
+      <c r="AJ129">
+        <v>2.1</v>
+      </c>
+      <c r="AK129">
+        <v>1.73</v>
+      </c>
+      <c r="AL129">
+        <v>1.22</v>
+      </c>
+      <c r="AM129">
+        <v>1.27</v>
+      </c>
+      <c r="AN129">
+        <v>1.7</v>
+      </c>
+      <c r="AO129">
+        <v>1.9</v>
+      </c>
+      <c r="AP129">
+        <v>1.64</v>
+      </c>
+      <c r="AQ129">
+        <v>1.82</v>
+      </c>
+      <c r="AR129">
+        <v>1.46</v>
+      </c>
+      <c r="AS129">
+        <v>1.35</v>
+      </c>
+      <c r="AT129">
+        <v>2.81</v>
+      </c>
+      <c r="AU129">
+        <v>3</v>
+      </c>
+      <c r="AV129">
+        <v>7</v>
+      </c>
+      <c r="AW129">
+        <v>8</v>
+      </c>
+      <c r="AX129">
+        <v>4</v>
+      </c>
+      <c r="AY129">
+        <v>11</v>
+      </c>
+      <c r="AZ129">
+        <v>11</v>
+      </c>
+      <c r="BA129">
+        <v>4</v>
+      </c>
+      <c r="BB129">
+        <v>3</v>
+      </c>
+      <c r="BC129">
+        <v>7</v>
+      </c>
+      <c r="BD129">
+        <v>2.55</v>
+      </c>
+      <c r="BE129">
+        <v>7.7</v>
+      </c>
+      <c r="BF129">
+        <v>1.68</v>
+      </c>
+      <c r="BG129">
+        <v>1.44</v>
+      </c>
+      <c r="BH129">
+        <v>2.43</v>
+      </c>
+      <c r="BI129">
+        <v>1.77</v>
+      </c>
+      <c r="BJ129">
+        <v>1.95</v>
+      </c>
+      <c r="BK129">
+        <v>2.35</v>
+      </c>
+      <c r="BL129">
+        <v>1.47</v>
+      </c>
+      <c r="BM129">
+        <v>3.28</v>
+      </c>
+      <c r="BN129">
+        <v>1.25</v>
+      </c>
+      <c r="BO129">
+        <v>4.33</v>
+      </c>
+      <c r="BP129">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7727625</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>79</v>
+      </c>
+      <c r="H130" t="s">
+        <v>72</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>3</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130" t="s">
+        <v>177</v>
+      </c>
+      <c r="P130" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q130">
+        <v>2.6</v>
+      </c>
+      <c r="R130">
+        <v>2.38</v>
+      </c>
+      <c r="S130">
+        <v>3.25</v>
+      </c>
+      <c r="T130">
+        <v>1.29</v>
+      </c>
+      <c r="U130">
+        <v>3.5</v>
+      </c>
+      <c r="V130">
+        <v>2.25</v>
+      </c>
+      <c r="W130">
+        <v>1.57</v>
+      </c>
+      <c r="X130">
+        <v>5</v>
+      </c>
+      <c r="Y130">
+        <v>1.14</v>
+      </c>
+      <c r="Z130">
+        <v>1.98</v>
+      </c>
+      <c r="AA130">
+        <v>3.25</v>
+      </c>
+      <c r="AB130">
+        <v>3.25</v>
+      </c>
+      <c r="AC130">
+        <v>1.01</v>
+      </c>
+      <c r="AD130">
+        <v>13</v>
+      </c>
+      <c r="AE130">
+        <v>1.12</v>
+      </c>
+      <c r="AF130">
+        <v>4.75</v>
+      </c>
+      <c r="AG130">
+        <v>1.45</v>
+      </c>
+      <c r="AH130">
+        <v>2.55</v>
+      </c>
+      <c r="AI130">
+        <v>1.44</v>
+      </c>
+      <c r="AJ130">
+        <v>2.63</v>
+      </c>
+      <c r="AK130">
+        <v>1.31</v>
+      </c>
+      <c r="AL130">
+        <v>1.27</v>
+      </c>
+      <c r="AM130">
+        <v>1.58</v>
+      </c>
+      <c r="AN130">
+        <v>1</v>
+      </c>
+      <c r="AO130">
+        <v>0.7</v>
+      </c>
+      <c r="AP130">
+        <v>1.18</v>
+      </c>
+      <c r="AQ130">
+        <v>0.64</v>
+      </c>
+      <c r="AR130">
+        <v>1.37</v>
+      </c>
+      <c r="AS130">
+        <v>1.52</v>
+      </c>
+      <c r="AT130">
+        <v>2.89</v>
+      </c>
+      <c r="AU130">
+        <v>12</v>
+      </c>
+      <c r="AV130">
+        <v>4</v>
+      </c>
+      <c r="AW130">
+        <v>9</v>
+      </c>
+      <c r="AX130">
+        <v>5</v>
+      </c>
+      <c r="AY130">
+        <v>21</v>
+      </c>
+      <c r="AZ130">
+        <v>9</v>
+      </c>
+      <c r="BA130">
+        <v>5</v>
+      </c>
+      <c r="BB130">
+        <v>2</v>
+      </c>
+      <c r="BC130">
+        <v>7</v>
+      </c>
+      <c r="BD130">
+        <v>1.61</v>
+      </c>
+      <c r="BE130">
+        <v>8.6</v>
+      </c>
+      <c r="BF130">
+        <v>2.62</v>
+      </c>
+      <c r="BG130">
+        <v>1.2</v>
+      </c>
+      <c r="BH130">
+        <v>4.2</v>
+      </c>
+      <c r="BI130">
+        <v>1.32</v>
+      </c>
+      <c r="BJ130">
+        <v>2.88</v>
+      </c>
+      <c r="BK130">
+        <v>1.57</v>
+      </c>
+      <c r="BL130">
+        <v>2.14</v>
+      </c>
+      <c r="BM130">
+        <v>1.95</v>
+      </c>
+      <c r="BN130">
+        <v>1.77</v>
+      </c>
+      <c r="BO130">
+        <v>2.56</v>
+      </c>
+      <c r="BP130">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7727627</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>70</v>
+      </c>
+      <c r="H131" t="s">
+        <v>77</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131" t="s">
+        <v>178</v>
+      </c>
+      <c r="P131" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q131">
+        <v>7</v>
+      </c>
+      <c r="R131">
+        <v>2.5</v>
+      </c>
+      <c r="S131">
+        <v>1.8</v>
+      </c>
+      <c r="T131">
+        <v>1.3</v>
+      </c>
+      <c r="U131">
+        <v>3.4</v>
+      </c>
+      <c r="V131">
+        <v>2.38</v>
+      </c>
+      <c r="W131">
+        <v>1.53</v>
+      </c>
+      <c r="X131">
+        <v>5</v>
+      </c>
+      <c r="Y131">
+        <v>1.14</v>
+      </c>
+      <c r="Z131">
+        <v>4.75</v>
+      </c>
+      <c r="AA131">
+        <v>3.9</v>
+      </c>
+      <c r="AB131">
+        <v>1.53</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>13</v>
+      </c>
+      <c r="AE131">
+        <v>1.16</v>
+      </c>
+      <c r="AF131">
+        <v>4.05</v>
+      </c>
+      <c r="AG131">
+        <v>1.75</v>
+      </c>
+      <c r="AH131">
+        <v>1.95</v>
+      </c>
+      <c r="AI131">
+        <v>2</v>
+      </c>
+      <c r="AJ131">
+        <v>1.73</v>
+      </c>
+      <c r="AK131">
+        <v>2.65</v>
+      </c>
+      <c r="AL131">
+        <v>1.12</v>
+      </c>
+      <c r="AM131">
+        <v>1.1</v>
+      </c>
+      <c r="AN131">
+        <v>1</v>
+      </c>
+      <c r="AO131">
+        <v>2.3</v>
+      </c>
+      <c r="AP131">
+        <v>0.91</v>
+      </c>
+      <c r="AQ131">
+        <v>2.36</v>
+      </c>
+      <c r="AR131">
+        <v>1.63</v>
+      </c>
+      <c r="AS131">
+        <v>1.66</v>
+      </c>
+      <c r="AT131">
+        <v>3.29</v>
+      </c>
+      <c r="AU131">
+        <v>4</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>2</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>6</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>9</v>
+      </c>
+      <c r="BC131">
+        <v>13</v>
+      </c>
+      <c r="BD131">
+        <v>3.05</v>
+      </c>
+      <c r="BE131">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF131">
+        <v>1.48</v>
+      </c>
+      <c r="BG131">
+        <v>1.18</v>
+      </c>
+      <c r="BH131">
+        <v>3.84</v>
+      </c>
+      <c r="BI131">
+        <v>1.37</v>
+      </c>
+      <c r="BJ131">
+        <v>2.66</v>
+      </c>
+      <c r="BK131">
+        <v>1.7</v>
+      </c>
+      <c r="BL131">
+        <v>2.05</v>
+      </c>
+      <c r="BM131">
+        <v>2.05</v>
+      </c>
+      <c r="BN131">
+        <v>1.7</v>
+      </c>
+      <c r="BO131">
+        <v>2.74</v>
+      </c>
+      <c r="BP131">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7727635</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45671.69791666666</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>81</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>2</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>85</v>
+      </c>
+      <c r="P132" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q132">
+        <v>5.5</v>
+      </c>
+      <c r="R132">
+        <v>2.6</v>
+      </c>
+      <c r="S132">
+        <v>1.83</v>
+      </c>
+      <c r="T132">
+        <v>1.25</v>
+      </c>
+      <c r="U132">
+        <v>3.75</v>
+      </c>
+      <c r="V132">
+        <v>2.1</v>
+      </c>
+      <c r="W132">
+        <v>1.67</v>
+      </c>
+      <c r="X132">
+        <v>4.5</v>
+      </c>
+      <c r="Y132">
+        <v>1.17</v>
+      </c>
+      <c r="Z132">
+        <v>6.5</v>
+      </c>
+      <c r="AA132">
+        <v>4.5</v>
+      </c>
+      <c r="AB132">
+        <v>1.33</v>
+      </c>
+      <c r="AC132">
+        <v>1.01</v>
+      </c>
+      <c r="AD132">
+        <v>17</v>
+      </c>
+      <c r="AE132">
+        <v>1.09</v>
+      </c>
+      <c r="AF132">
+        <v>5.4</v>
+      </c>
+      <c r="AG132">
+        <v>1.44</v>
+      </c>
+      <c r="AH132">
+        <v>2.63</v>
+      </c>
+      <c r="AI132">
+        <v>1.62</v>
+      </c>
+      <c r="AJ132">
+        <v>2.2</v>
+      </c>
+      <c r="AK132">
+        <v>2.5</v>
+      </c>
+      <c r="AL132">
+        <v>1.14</v>
+      </c>
+      <c r="AM132">
+        <v>1.1</v>
+      </c>
+      <c r="AN132">
+        <v>1.6</v>
+      </c>
+      <c r="AO132">
+        <v>2.1</v>
+      </c>
+      <c r="AP132">
+        <v>1.45</v>
+      </c>
+      <c r="AQ132">
+        <v>2.18</v>
+      </c>
+      <c r="AR132">
+        <v>1.5</v>
+      </c>
+      <c r="AS132">
+        <v>2.25</v>
+      </c>
+      <c r="AT132">
+        <v>3.75</v>
+      </c>
+      <c r="AU132">
+        <v>2</v>
+      </c>
+      <c r="AV132">
+        <v>8</v>
+      </c>
+      <c r="AW132">
+        <v>3</v>
+      </c>
+      <c r="AX132">
+        <v>9</v>
+      </c>
+      <c r="AY132">
+        <v>5</v>
+      </c>
+      <c r="AZ132">
+        <v>17</v>
+      </c>
+      <c r="BA132">
+        <v>1</v>
+      </c>
+      <c r="BB132">
+        <v>4</v>
+      </c>
+      <c r="BC132">
+        <v>5</v>
+      </c>
+      <c r="BD132">
+        <v>5.75</v>
+      </c>
+      <c r="BE132">
+        <v>11</v>
+      </c>
+      <c r="BF132">
+        <v>1.17</v>
+      </c>
+      <c r="BG132">
+        <v>1.25</v>
+      </c>
+      <c r="BH132">
+        <v>3.28</v>
+      </c>
+      <c r="BI132">
+        <v>1.48</v>
+      </c>
+      <c r="BJ132">
+        <v>2.33</v>
+      </c>
+      <c r="BK132">
+        <v>1.8</v>
+      </c>
+      <c r="BL132">
+        <v>1.91</v>
+      </c>
+      <c r="BM132">
+        <v>2.35</v>
+      </c>
+      <c r="BN132">
+        <v>1.47</v>
+      </c>
+      <c r="BO132">
+        <v>3.14</v>
+      </c>
+      <c r="BP132">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -756,6 +756,9 @@
   <si>
     <t>['39', '89']</t>
   </si>
+  <si>
+    <t>['59', '65']</t>
+  </si>
 </sst>
 </file>
 
@@ -1116,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1659,7 +1662,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ3">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2068,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5">
         <v>1.82</v>
@@ -4749,7 +4752,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ18">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR18">
         <v>1.22</v>
@@ -7424,7 +7427,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
         <v>1.09</v>
@@ -9278,7 +9281,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ40">
         <v>2.36</v>
@@ -10720,7 +10723,7 @@
         <v>1.25</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
         <v>0.82</v>
@@ -11341,7 +11344,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR50">
         <v>3.27</v>
@@ -12783,7 +12786,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR57">
         <v>1.02</v>
@@ -13192,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
         <v>0.27</v>
@@ -15255,7 +15258,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ69">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR69">
         <v>1.56</v>
@@ -17109,7 +17112,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ78">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR78">
         <v>1.99</v>
@@ -17930,7 +17933,7 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ82">
         <v>0.82</v>
@@ -18136,7 +18139,7 @@
         <v>2.4</v>
       </c>
       <c r="AP83">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83">
         <v>2.18</v>
@@ -18551,7 +18554,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR85">
         <v>1.83</v>
@@ -18960,7 +18963,7 @@
         <v>1.88</v>
       </c>
       <c r="AP87">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>1.45</v>
@@ -20405,7 +20408,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ94">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR94">
         <v>1.18</v>
@@ -21641,7 +21644,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.39</v>
@@ -22462,7 +22465,7 @@
         <v>2.13</v>
       </c>
       <c r="AP104">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>1.91</v>
@@ -24731,7 +24734,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR115">
         <v>1.04</v>
@@ -25140,7 +25143,7 @@
         <v>0.78</v>
       </c>
       <c r="AP117">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117">
         <v>0.64</v>
@@ -28309,6 +28312,212 @@
       </c>
       <c r="BP132">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7727626</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45674.69791666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>73</v>
+      </c>
+      <c r="H133" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>2</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>85</v>
+      </c>
+      <c r="P133" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q133">
+        <v>2.75</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>3.6</v>
+      </c>
+      <c r="T133">
+        <v>1.4</v>
+      </c>
+      <c r="U133">
+        <v>2.75</v>
+      </c>
+      <c r="V133">
+        <v>2.75</v>
+      </c>
+      <c r="W133">
+        <v>1.4</v>
+      </c>
+      <c r="X133">
+        <v>7</v>
+      </c>
+      <c r="Y133">
+        <v>1.08</v>
+      </c>
+      <c r="Z133">
+        <v>2.02</v>
+      </c>
+      <c r="AA133">
+        <v>3.4</v>
+      </c>
+      <c r="AB133">
+        <v>3.6</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>9</v>
+      </c>
+      <c r="AE133">
+        <v>1.24</v>
+      </c>
+      <c r="AF133">
+        <v>3.34</v>
+      </c>
+      <c r="AG133">
+        <v>1.95</v>
+      </c>
+      <c r="AH133">
+        <v>1.82</v>
+      </c>
+      <c r="AI133">
+        <v>1.73</v>
+      </c>
+      <c r="AJ133">
+        <v>2</v>
+      </c>
+      <c r="AK133">
+        <v>1.31</v>
+      </c>
+      <c r="AL133">
+        <v>1.28</v>
+      </c>
+      <c r="AM133">
+        <v>1.59</v>
+      </c>
+      <c r="AN133">
+        <v>1.4</v>
+      </c>
+      <c r="AO133">
+        <v>1.2</v>
+      </c>
+      <c r="AP133">
+        <v>1.27</v>
+      </c>
+      <c r="AQ133">
+        <v>1.36</v>
+      </c>
+      <c r="AR133">
+        <v>1.54</v>
+      </c>
+      <c r="AS133">
+        <v>1.37</v>
+      </c>
+      <c r="AT133">
+        <v>2.91</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>8</v>
+      </c>
+      <c r="AW133">
+        <v>10</v>
+      </c>
+      <c r="AX133">
+        <v>3</v>
+      </c>
+      <c r="AY133">
+        <v>14</v>
+      </c>
+      <c r="AZ133">
+        <v>11</v>
+      </c>
+      <c r="BA133">
+        <v>4</v>
+      </c>
+      <c r="BB133">
+        <v>6</v>
+      </c>
+      <c r="BC133">
+        <v>10</v>
+      </c>
+      <c r="BD133">
+        <v>1.5</v>
+      </c>
+      <c r="BE133">
+        <v>8.6</v>
+      </c>
+      <c r="BF133">
+        <v>2.99</v>
+      </c>
+      <c r="BG133">
+        <v>1.23</v>
+      </c>
+      <c r="BH133">
+        <v>3.42</v>
+      </c>
+      <c r="BI133">
+        <v>1.45</v>
+      </c>
+      <c r="BJ133">
+        <v>2.41</v>
+      </c>
+      <c r="BK133">
+        <v>1.77</v>
+      </c>
+      <c r="BL133">
+        <v>1.95</v>
+      </c>
+      <c r="BM133">
+        <v>2.3</v>
+      </c>
+      <c r="BN133">
+        <v>1.49</v>
+      </c>
+      <c r="BO133">
+        <v>3.08</v>
+      </c>
+      <c r="BP133">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,10 +505,10 @@
     <t>['46', '54']</t>
   </si>
   <si>
-    <t>['35', '44', '82']</t>
+    <t>['83', '88']</t>
   </si>
   <si>
-    <t>['83', '88']</t>
+    <t>['35', '44', '82']</t>
   </si>
   <si>
     <t>['37', '70', '89']</t>
@@ -523,10 +523,10 @@
     <t>['22']</t>
   </si>
   <si>
-    <t>['21', '24', '29', '31', '39', '44', '63']</t>
+    <t>['5', '18']</t>
   </si>
   <si>
-    <t>['5', '18']</t>
+    <t>['21', '24', '29', '31', '39', '44', '63']</t>
   </si>
   <si>
     <t>['27', '36']</t>
@@ -538,19 +538,19 @@
     <t>['53', '87']</t>
   </si>
   <si>
-    <t>['63', '90+9']</t>
-  </si>
-  <si>
     <t>['43', '51', '55', '62', '63']</t>
   </si>
   <si>
-    <t>['47', '80', '84']</t>
+    <t>['63', '90+9']</t>
   </si>
   <si>
     <t>['24']</t>
   </si>
   <si>
     <t>['51']</t>
+  </si>
+  <si>
+    <t>['47', '80', '84']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -730,13 +730,13 @@
     <t>['25', '70', '83']</t>
   </si>
   <si>
-    <t>['10', '71']</t>
+    <t>['2', '11', '40', '73', '74']</t>
   </si>
   <si>
     <t>['33', '69']</t>
   </si>
   <si>
-    <t>['2', '11', '40', '73', '74']</t>
+    <t>['10', '71']</t>
   </si>
   <si>
     <t>['63', '70']</t>
@@ -752,6 +752,9 @@
   </si>
   <si>
     <t>['5', '47']</t>
+  </si>
+  <si>
+    <t>['39', '89']</t>
   </si>
   <si>
     <t>['59', '65']</t>
@@ -1116,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2483,7 +2486,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ7">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR7">
         <v>1.59</v>
@@ -2686,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8">
         <v>1.09</v>
@@ -5158,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ20">
         <v>1.82</v>
@@ -7427,7 +7430,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ31">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -9487,7 +9490,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ41">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR41">
         <v>2.47</v>
@@ -10102,7 +10105,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ44">
         <v>1.09</v>
@@ -12165,7 +12168,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ54">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR54">
         <v>1.83</v>
@@ -14016,7 +14019,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ63">
         <v>1.91</v>
@@ -16282,7 +16285,7 @@
         <v>2.67</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
         <v>2.36</v>
@@ -16900,7 +16903,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ77">
         <v>0.82</v>
@@ -17727,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -18139,7 +18142,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18345,7 +18348,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ84">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -20402,7 +20405,7 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ94">
         <v>1.36</v>
@@ -20817,7 +20820,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ96">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -21020,7 +21023,7 @@
         <v>0.38</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ97">
         <v>0.27</v>
@@ -22671,7 +22674,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ105">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -23166,7 +23169,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>7727594</v>
+        <v>7727610</v>
       </c>
       <c r="C108" t="s">
         <v>68</v>
@@ -23178,58 +23181,58 @@
         <v>45640.47916666666</v>
       </c>
       <c r="F108">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O108" t="s">
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="Q108">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R108">
         <v>2.3</v>
       </c>
       <c r="S108">
+        <v>4.75</v>
+      </c>
+      <c r="T108">
+        <v>1.33</v>
+      </c>
+      <c r="U108">
         <v>3.25</v>
       </c>
-      <c r="T108">
-        <v>1.3</v>
-      </c>
-      <c r="U108">
-        <v>3.4</v>
-      </c>
       <c r="V108">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="W108">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X108">
         <v>5.5</v>
@@ -23238,94 +23241,94 @@
         <v>1.13</v>
       </c>
       <c r="Z108">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AA108">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB108">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AC108">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AD108">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE108">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG108">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH108">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AI108">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ108">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AK108">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AL108">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AM108">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AN108">
+        <v>1.63</v>
+      </c>
+      <c r="AO108">
         <v>0.88</v>
       </c>
-      <c r="AO108">
-        <v>1.38</v>
-      </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
-        <v>1.09</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AS108">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AT108">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AU108">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AV108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW108">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY108">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ108">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA108">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BB108">
         <v>3</v>
       </c>
       <c r="BC108">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BD108">
         <v>0</v>
@@ -23372,7 +23375,7 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>7727610</v>
+        <v>7727594</v>
       </c>
       <c r="C109" t="s">
         <v>68</v>
@@ -23384,58 +23387,58 @@
         <v>45640.47916666666</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G109" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O109" t="s">
         <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="Q109">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R109">
         <v>2.3</v>
       </c>
       <c r="S109">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="T109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U109">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V109">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="W109">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X109">
         <v>5.5</v>
@@ -23444,94 +23447,94 @@
         <v>1.13</v>
       </c>
       <c r="Z109">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA109">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB109">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC109">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD109">
+        <v>16</v>
+      </c>
+      <c r="AE109">
+        <v>1.16</v>
+      </c>
+      <c r="AF109">
+        <v>5</v>
+      </c>
+      <c r="AG109">
+        <v>1.57</v>
+      </c>
+      <c r="AH109">
+        <v>2.25</v>
+      </c>
+      <c r="AI109">
+        <v>1.53</v>
+      </c>
+      <c r="AJ109">
+        <v>2.38</v>
+      </c>
+      <c r="AK109">
+        <v>1.28</v>
+      </c>
+      <c r="AL109">
+        <v>1.23</v>
+      </c>
+      <c r="AM109">
+        <v>1.59</v>
+      </c>
+      <c r="AN109">
+        <v>0.88</v>
+      </c>
+      <c r="AO109">
+        <v>1.38</v>
+      </c>
+      <c r="AP109">
+        <v>1.18</v>
+      </c>
+      <c r="AQ109">
+        <v>1.09</v>
+      </c>
+      <c r="AR109">
+        <v>1.33</v>
+      </c>
+      <c r="AS109">
+        <v>1.32</v>
+      </c>
+      <c r="AT109">
+        <v>2.65</v>
+      </c>
+      <c r="AU109">
         <v>11</v>
       </c>
-      <c r="AE109">
-        <v>1.22</v>
-      </c>
-      <c r="AF109">
-        <v>4</v>
-      </c>
-      <c r="AG109">
-        <v>1.7</v>
-      </c>
-      <c r="AH109">
-        <v>2.05</v>
-      </c>
-      <c r="AI109">
-        <v>1.73</v>
-      </c>
-      <c r="AJ109">
-        <v>2</v>
-      </c>
-      <c r="AK109">
-        <v>1.19</v>
-      </c>
-      <c r="AL109">
-        <v>1.21</v>
-      </c>
-      <c r="AM109">
-        <v>1.81</v>
-      </c>
-      <c r="AN109">
-        <v>1.63</v>
-      </c>
-      <c r="AO109">
-        <v>0.88</v>
-      </c>
-      <c r="AP109">
-        <v>1.6</v>
-      </c>
-      <c r="AQ109">
-        <v>0.64</v>
-      </c>
-      <c r="AR109">
-        <v>1.26</v>
-      </c>
-      <c r="AS109">
-        <v>1.45</v>
-      </c>
-      <c r="AT109">
-        <v>2.71</v>
-      </c>
-      <c r="AU109">
+      <c r="AV109">
+        <v>7</v>
+      </c>
+      <c r="AW109">
+        <v>3</v>
+      </c>
+      <c r="AX109">
+        <v>5</v>
+      </c>
+      <c r="AY109">
+        <v>18</v>
+      </c>
+      <c r="AZ109">
         <v>15</v>
       </c>
-      <c r="AV109">
-        <v>8</v>
-      </c>
-      <c r="AW109">
-        <v>6</v>
-      </c>
-      <c r="AX109">
-        <v>6</v>
-      </c>
-      <c r="AY109">
-        <v>21</v>
-      </c>
-      <c r="AZ109">
-        <v>14</v>
-      </c>
       <c r="BA109">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BB109">
         <v>3</v>
       </c>
       <c r="BC109">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BD109">
         <v>0</v>
@@ -24522,7 +24525,7 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114">
         <v>0.82</v>
@@ -24608,7 +24611,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7727617</v>
+        <v>7727615</v>
       </c>
       <c r="C115" t="s">
         <v>68</v>
@@ -24623,190 +24626,190 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H115" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M115">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="P115" t="s">
         <v>238</v>
       </c>
       <c r="Q115">
+        <v>6</v>
+      </c>
+      <c r="R115">
+        <v>2.6</v>
+      </c>
+      <c r="S115">
+        <v>1.8</v>
+      </c>
+      <c r="T115">
+        <v>1.25</v>
+      </c>
+      <c r="U115">
         <v>3.75</v>
       </c>
-      <c r="R115">
+      <c r="V115">
         <v>2.1</v>
       </c>
-      <c r="S115">
-        <v>2.75</v>
-      </c>
-      <c r="T115">
-        <v>1.4</v>
-      </c>
-      <c r="U115">
-        <v>2.75</v>
-      </c>
-      <c r="V115">
-        <v>3</v>
-      </c>
       <c r="W115">
+        <v>1.67</v>
+      </c>
+      <c r="X115">
+        <v>4.33</v>
+      </c>
+      <c r="Y115">
+        <v>1.2</v>
+      </c>
+      <c r="Z115">
+        <v>6</v>
+      </c>
+      <c r="AA115">
+        <v>4.75</v>
+      </c>
+      <c r="AB115">
         <v>1.36</v>
-      </c>
-      <c r="X115">
-        <v>7</v>
-      </c>
-      <c r="Y115">
-        <v>1.08</v>
-      </c>
-      <c r="Z115">
-        <v>3.4</v>
-      </c>
-      <c r="AA115">
-        <v>3.4</v>
-      </c>
-      <c r="AB115">
-        <v>1.9</v>
       </c>
       <c r="AC115">
         <v>1.01</v>
       </c>
       <c r="AD115">
-        <v>8.699999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AE115">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="AG115">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AH115">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI115">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ115">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK115">
-        <v>1.64</v>
+        <v>2.83</v>
       </c>
       <c r="AL115">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AM115">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AN115">
         <v>1.11</v>
       </c>
       <c r="AO115">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AP115">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="AQ115">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AR115">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AS115">
+        <v>2.24</v>
+      </c>
+      <c r="AT115">
+        <v>3.64</v>
+      </c>
+      <c r="AU115">
+        <v>5</v>
+      </c>
+      <c r="AV115">
+        <v>12</v>
+      </c>
+      <c r="AW115">
+        <v>3</v>
+      </c>
+      <c r="AX115">
+        <v>6</v>
+      </c>
+      <c r="AY115">
+        <v>11</v>
+      </c>
+      <c r="AZ115">
+        <v>23</v>
+      </c>
+      <c r="BA115">
+        <v>6</v>
+      </c>
+      <c r="BB115">
+        <v>6</v>
+      </c>
+      <c r="BC115">
+        <v>12</v>
+      </c>
+      <c r="BD115">
+        <v>6.5</v>
+      </c>
+      <c r="BE115">
+        <v>12.25</v>
+      </c>
+      <c r="BF115">
+        <v>1.13</v>
+      </c>
+      <c r="BG115">
+        <v>1.21</v>
+      </c>
+      <c r="BH115">
+        <v>4.15</v>
+      </c>
+      <c r="BI115">
         <v>1.33</v>
       </c>
-      <c r="AT115">
-        <v>3.01</v>
-      </c>
-      <c r="AU115">
-        <v>2</v>
-      </c>
-      <c r="AV115">
-        <v>6</v>
-      </c>
-      <c r="AW115">
-        <v>7</v>
-      </c>
-      <c r="AX115">
-        <v>4</v>
-      </c>
-      <c r="AY115">
-        <v>9</v>
-      </c>
-      <c r="AZ115">
-        <v>11</v>
-      </c>
-      <c r="BA115">
-        <v>4</v>
-      </c>
-      <c r="BB115">
-        <v>3</v>
-      </c>
-      <c r="BC115">
-        <v>7</v>
-      </c>
-      <c r="BD115">
-        <v>2.96</v>
-      </c>
-      <c r="BE115">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF115">
-        <v>1.52</v>
-      </c>
-      <c r="BG115">
+      <c r="BJ115">
+        <v>2.83</v>
+      </c>
+      <c r="BK115">
+        <v>1.59</v>
+      </c>
+      <c r="BL115">
+        <v>2.1</v>
+      </c>
+      <c r="BM115">
+        <v>2.05</v>
+      </c>
+      <c r="BN115">
+        <v>1.7</v>
+      </c>
+      <c r="BO115">
+        <v>2.56</v>
+      </c>
+      <c r="BP115">
         <v>1.4</v>
-      </c>
-      <c r="BH115">
-        <v>2.8</v>
-      </c>
-      <c r="BI115">
-        <v>1.68</v>
-      </c>
-      <c r="BJ115">
-        <v>2.11</v>
-      </c>
-      <c r="BK115">
-        <v>2.12</v>
-      </c>
-      <c r="BL115">
-        <v>1.67</v>
-      </c>
-      <c r="BM115">
-        <v>2.77</v>
-      </c>
-      <c r="BN115">
-        <v>1.41</v>
-      </c>
-      <c r="BO115">
-        <v>3.85</v>
-      </c>
-      <c r="BP115">
-        <v>1.24</v>
       </c>
     </row>
     <row r="116" spans="1:68">
@@ -25059,7 +25062,7 @@
         <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P117" t="s">
         <v>239</v>
@@ -25226,7 +25229,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7727615</v>
+        <v>7727617</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25241,190 +25244,190 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H118" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N118">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O118" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="P118" t="s">
         <v>240</v>
       </c>
       <c r="Q118">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R118">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="T118">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U118">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="W118">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="X118">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="Y118">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z118">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AA118">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB118">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AC118">
         <v>1.01</v>
       </c>
       <c r="AD118">
-        <v>19.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF118">
-        <v>5.1</v>
+        <v>3.22</v>
       </c>
       <c r="AG118">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AH118">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI118">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ118">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK118">
-        <v>2.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL118">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AM118">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AN118">
         <v>1.11</v>
       </c>
       <c r="AO118">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>0.91</v>
       </c>
       <c r="AQ118">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AR118">
+        <v>1.68</v>
+      </c>
+      <c r="AS118">
+        <v>1.33</v>
+      </c>
+      <c r="AT118">
+        <v>3.01</v>
+      </c>
+      <c r="AU118">
+        <v>2</v>
+      </c>
+      <c r="AV118">
+        <v>6</v>
+      </c>
+      <c r="AW118">
+        <v>7</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
+        <v>9</v>
+      </c>
+      <c r="AZ118">
+        <v>11</v>
+      </c>
+      <c r="BA118">
+        <v>4</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>7</v>
+      </c>
+      <c r="BD118">
+        <v>2.96</v>
+      </c>
+      <c r="BE118">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF118">
+        <v>1.52</v>
+      </c>
+      <c r="BG118">
         <v>1.4</v>
       </c>
-      <c r="AS118">
-        <v>2.24</v>
-      </c>
-      <c r="AT118">
-        <v>3.64</v>
-      </c>
-      <c r="AU118">
-        <v>5</v>
-      </c>
-      <c r="AV118">
-        <v>12</v>
-      </c>
-      <c r="AW118">
-        <v>3</v>
-      </c>
-      <c r="AX118">
-        <v>6</v>
-      </c>
-      <c r="AY118">
-        <v>11</v>
-      </c>
-      <c r="AZ118">
-        <v>23</v>
-      </c>
-      <c r="BA118">
-        <v>6</v>
-      </c>
-      <c r="BB118">
-        <v>6</v>
-      </c>
-      <c r="BC118">
-        <v>12</v>
-      </c>
-      <c r="BD118">
-        <v>6.5</v>
-      </c>
-      <c r="BE118">
-        <v>12.25</v>
-      </c>
-      <c r="BF118">
-        <v>1.13</v>
-      </c>
-      <c r="BG118">
-        <v>1.21</v>
-      </c>
       <c r="BH118">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="BI118">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="BJ118">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="BK118">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="BL118">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="BM118">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="BN118">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="BO118">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="BP118">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -26462,7 +26465,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7727607</v>
+        <v>7727606</v>
       </c>
       <c r="C124" t="s">
         <v>68</v>
@@ -26477,190 +26480,190 @@
         <v>19</v>
       </c>
       <c r="G124" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124">
         <v>1</v>
       </c>
       <c r="K124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M124">
         <v>1</v>
       </c>
       <c r="N124">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O124" t="s">
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="Q124">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="R124">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="S124">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T124">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U124">
+        <v>3.25</v>
+      </c>
+      <c r="V124">
+        <v>2.5</v>
+      </c>
+      <c r="W124">
+        <v>1.5</v>
+      </c>
+      <c r="X124">
+        <v>5.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.13</v>
+      </c>
+      <c r="Z124">
+        <v>1.38</v>
+      </c>
+      <c r="AA124">
         <v>4.33</v>
       </c>
-      <c r="V124">
-        <v>1.83</v>
-      </c>
-      <c r="W124">
-        <v>1.83</v>
-      </c>
-      <c r="X124">
-        <v>3.75</v>
-      </c>
-      <c r="Y124">
-        <v>1.25</v>
-      </c>
-      <c r="Z124">
-        <v>1.13</v>
-      </c>
-      <c r="AA124">
-        <v>8.5</v>
-      </c>
       <c r="AB124">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AC124">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD124">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE124">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AF124">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG124">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH124">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AI124">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AJ124">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK124">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AL124">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AM124">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AN124">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AO124">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="AP124">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AQ124">
         <v>0.82</v>
       </c>
       <c r="AR124">
-        <v>2.58</v>
+        <v>1.41</v>
       </c>
       <c r="AS124">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AT124">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AU124">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV124">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW124">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY124">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="AZ124">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA124">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BB124">
         <v>0</v>
       </c>
       <c r="BC124">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BD124">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="BE124">
-        <v>17.75</v>
+        <v>10.25</v>
       </c>
       <c r="BF124">
-        <v>12.75</v>
+        <v>5.15</v>
       </c>
       <c r="BG124">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BH124">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="BI124">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="BJ124">
-        <v>3.44</v>
+        <v>2.29</v>
       </c>
       <c r="BK124">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="BL124">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="BM124">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="BN124">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="BO124">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="BP124">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="125" spans="1:68">
@@ -26668,7 +26671,7 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>7727606</v>
+        <v>7727611</v>
       </c>
       <c r="C125" t="s">
         <v>68</v>
@@ -26683,82 +26686,82 @@
         <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L125">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="P125" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="Q125">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="R125">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S125">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="T125">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U125">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V125">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W125">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X125">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y125">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z125">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AA125">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AB125">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AC125">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD125">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE125">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF125">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG125">
         <v>1.73</v>
@@ -26767,106 +26770,106 @@
         <v>2</v>
       </c>
       <c r="AI125">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ125">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AK125">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AL125">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AM125">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="AN125">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AO125">
-        <v>0.67</v>
+        <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AQ125">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
-        <v>1.41</v>
+        <v>1.81</v>
       </c>
       <c r="AS125">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AT125">
-        <v>2.74</v>
+        <v>3.27</v>
       </c>
       <c r="AU125">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
         <v>5</v>
       </c>
-      <c r="AW125">
-        <v>7</v>
-      </c>
       <c r="AX125">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY125">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ125">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA125">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB125">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC125">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD125">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BE125">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="BF125">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BG125">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BH125">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BI125">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BJ125">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BK125">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BL125">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BM125">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BN125">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BO125">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="BP125">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:68">
@@ -26874,7 +26877,7 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>7727611</v>
+        <v>7727607</v>
       </c>
       <c r="C126" t="s">
         <v>68</v>
@@ -26889,190 +26892,190 @@
         <v>19</v>
       </c>
       <c r="G126" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I126">
         <v>0</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O126" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="Q126">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R126">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S126">
-        <v>4.75</v>
+        <v>11</v>
       </c>
       <c r="T126">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="U126">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="V126">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="W126">
+        <v>1.83</v>
+      </c>
+      <c r="X126">
+        <v>3.75</v>
+      </c>
+      <c r="Y126">
+        <v>1.25</v>
+      </c>
+      <c r="Z126">
+        <v>1.13</v>
+      </c>
+      <c r="AA126">
+        <v>8.5</v>
+      </c>
+      <c r="AB126">
+        <v>13</v>
+      </c>
+      <c r="AC126">
+        <v>1</v>
+      </c>
+      <c r="AD126">
+        <v>23</v>
+      </c>
+      <c r="AE126">
+        <v>1.01</v>
+      </c>
+      <c r="AF126">
+        <v>7.7</v>
+      </c>
+      <c r="AG126">
+        <v>1.3</v>
+      </c>
+      <c r="AH126">
+        <v>3.4</v>
+      </c>
+      <c r="AI126">
+        <v>2.1</v>
+      </c>
+      <c r="AJ126">
+        <v>1.67</v>
+      </c>
+      <c r="AK126">
+        <v>1.01</v>
+      </c>
+      <c r="AL126">
+        <v>1.02</v>
+      </c>
+      <c r="AM126">
+        <v>4</v>
+      </c>
+      <c r="AN126">
+        <v>2.4</v>
+      </c>
+      <c r="AO126">
+        <v>0.9</v>
+      </c>
+      <c r="AP126">
+        <v>2.45</v>
+      </c>
+      <c r="AQ126">
+        <v>0.82</v>
+      </c>
+      <c r="AR126">
+        <v>2.58</v>
+      </c>
+      <c r="AS126">
+        <v>1.32</v>
+      </c>
+      <c r="AT126">
+        <v>3.9</v>
+      </c>
+      <c r="AU126">
+        <v>11</v>
+      </c>
+      <c r="AV126">
+        <v>4</v>
+      </c>
+      <c r="AW126">
+        <v>11</v>
+      </c>
+      <c r="AX126">
+        <v>1</v>
+      </c>
+      <c r="AY126">
+        <v>35</v>
+      </c>
+      <c r="AZ126">
+        <v>5</v>
+      </c>
+      <c r="BA126">
+        <v>16</v>
+      </c>
+      <c r="BB126">
+        <v>0</v>
+      </c>
+      <c r="BC126">
+        <v>16</v>
+      </c>
+      <c r="BD126">
+        <v>1.02</v>
+      </c>
+      <c r="BE126">
+        <v>17.75</v>
+      </c>
+      <c r="BF126">
+        <v>12.75</v>
+      </c>
+      <c r="BG126">
+        <v>1.15</v>
+      </c>
+      <c r="BH126">
+        <v>5</v>
+      </c>
+      <c r="BI126">
+        <v>1.21</v>
+      </c>
+      <c r="BJ126">
+        <v>3.44</v>
+      </c>
+      <c r="BK126">
         <v>1.4</v>
       </c>
-      <c r="X126">
-        <v>6.5</v>
-      </c>
-      <c r="Y126">
-        <v>1.1</v>
-      </c>
-      <c r="Z126">
-        <v>1.75</v>
-      </c>
-      <c r="AA126">
-        <v>3.75</v>
-      </c>
-      <c r="AB126">
-        <v>3.8</v>
-      </c>
-      <c r="AC126">
-        <v>1.04</v>
-      </c>
-      <c r="AD126">
-        <v>11</v>
-      </c>
-      <c r="AE126">
-        <v>1.27</v>
-      </c>
-      <c r="AF126">
-        <v>3.5</v>
-      </c>
-      <c r="AG126">
-        <v>1.73</v>
-      </c>
-      <c r="AH126">
-        <v>2</v>
-      </c>
-      <c r="AI126">
-        <v>1.83</v>
-      </c>
-      <c r="AJ126">
-        <v>1.83</v>
-      </c>
-      <c r="AK126">
-        <v>1.15</v>
-      </c>
-      <c r="AL126">
-        <v>1.21</v>
-      </c>
-      <c r="AM126">
-        <v>1.9</v>
-      </c>
-      <c r="AN126">
+      <c r="BL126">
+        <v>2.48</v>
+      </c>
+      <c r="BM126">
+        <v>1.77</v>
+      </c>
+      <c r="BN126">
+        <v>1.95</v>
+      </c>
+      <c r="BO126">
         <v>2.1</v>
       </c>
-      <c r="AO126">
-        <v>1.2</v>
-      </c>
-      <c r="AP126">
-        <v>2.18</v>
-      </c>
-      <c r="AQ126">
-        <v>1.09</v>
-      </c>
-      <c r="AR126">
-        <v>1.81</v>
-      </c>
-      <c r="AS126">
-        <v>1.46</v>
-      </c>
-      <c r="AT126">
-        <v>3.27</v>
-      </c>
-      <c r="AU126">
-        <v>4</v>
-      </c>
-      <c r="AV126">
-        <v>3</v>
-      </c>
-      <c r="AW126">
-        <v>5</v>
-      </c>
-      <c r="AX126">
-        <v>8</v>
-      </c>
-      <c r="AY126">
-        <v>11</v>
-      </c>
-      <c r="AZ126">
-        <v>15</v>
-      </c>
-      <c r="BA126">
-        <v>4</v>
-      </c>
-      <c r="BB126">
-        <v>5</v>
-      </c>
-      <c r="BC126">
-        <v>9</v>
-      </c>
-      <c r="BD126">
-        <v>0</v>
-      </c>
-      <c r="BE126">
-        <v>0</v>
-      </c>
-      <c r="BF126">
-        <v>0</v>
-      </c>
-      <c r="BG126">
-        <v>0</v>
-      </c>
-      <c r="BH126">
-        <v>0</v>
-      </c>
-      <c r="BI126">
-        <v>0</v>
-      </c>
-      <c r="BJ126">
-        <v>0</v>
-      </c>
-      <c r="BK126">
-        <v>0</v>
-      </c>
-      <c r="BL126">
-        <v>0</v>
-      </c>
-      <c r="BM126">
-        <v>0</v>
-      </c>
-      <c r="BN126">
-        <v>0</v>
-      </c>
-      <c r="BO126">
-        <v>0</v>
-      </c>
       <c r="BP126">
-        <v>0</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="127" spans="1:68">
@@ -27492,7 +27495,7 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>7727625</v>
+        <v>7727634</v>
       </c>
       <c r="C129" t="s">
         <v>68</v>
@@ -27507,190 +27510,190 @@
         <v>22</v>
       </c>
       <c r="G129" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O129" t="s">
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="Q129">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R129">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S129">
+        <v>2.4</v>
+      </c>
+      <c r="T129">
+        <v>1.33</v>
+      </c>
+      <c r="U129">
         <v>3.25</v>
       </c>
-      <c r="T129">
-        <v>1.29</v>
-      </c>
-      <c r="U129">
-        <v>3.5</v>
-      </c>
       <c r="V129">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="W129">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="X129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y129">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA129">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AB129">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC129">
         <v>1.01</v>
       </c>
       <c r="AD129">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE129">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF129">
-        <v>4.75</v>
+        <v>3.68</v>
       </c>
       <c r="AG129">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AH129">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI129">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AJ129">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK129">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AL129">
+        <v>1.22</v>
+      </c>
+      <c r="AM129">
         <v>1.27</v>
       </c>
-      <c r="AM129">
-        <v>1.58</v>
-      </c>
       <c r="AN129">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AO129">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="AP129">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="AQ129">
-        <v>0.64</v>
+        <v>1.82</v>
       </c>
       <c r="AR129">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AS129">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AT129">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AU129">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AV129">
+        <v>7</v>
+      </c>
+      <c r="AW129">
+        <v>8</v>
+      </c>
+      <c r="AX129">
         <v>4</v>
       </c>
-      <c r="AW129">
-        <v>9</v>
-      </c>
-      <c r="AX129">
-        <v>5</v>
-      </c>
       <c r="AY129">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC129">
         <v>7</v>
       </c>
       <c r="BD129">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="BE129">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="BF129">
-        <v>2.62</v>
+        <v>1.68</v>
       </c>
       <c r="BG129">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="BH129">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="BI129">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="BJ129">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="BK129">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="BL129">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="BM129">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="BN129">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="BO129">
-        <v>2.56</v>
+        <v>4.33</v>
       </c>
       <c r="BP129">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="130" spans="1:68">
@@ -27698,7 +27701,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7727634</v>
+        <v>7727627</v>
       </c>
       <c r="C130" t="s">
         <v>68</v>
@@ -27713,190 +27716,190 @@
         <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H130" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130">
         <v>1</v>
       </c>
       <c r="K130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L130">
         <v>1</v>
       </c>
       <c r="M130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O130" t="s">
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>94</v>
+        <v>245</v>
       </c>
       <c r="Q130">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R130">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S130">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="T130">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U130">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V130">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="W130">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y130">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z130">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA130">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB130">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC130">
         <v>1.01</v>
       </c>
       <c r="AD130">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AE130">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF130">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="AG130">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH130">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AI130">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AJ130">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK130">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AL130">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AM130">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AN130">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AO130">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AP130">
-        <v>1.64</v>
+        <v>0.91</v>
       </c>
       <c r="AQ130">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AR130">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AS130">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AT130">
-        <v>2.81</v>
+        <v>3.29</v>
       </c>
       <c r="AU130">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV130">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW130">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AX130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY130">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA130">
         <v>4</v>
       </c>
       <c r="BB130">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BC130">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD130">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="BE130">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF130">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="BG130">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="BH130">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="BI130">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="BJ130">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="BK130">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="BL130">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="BM130">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="BN130">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="BO130">
-        <v>4.33</v>
+        <v>2.74</v>
       </c>
       <c r="BP130">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="131" spans="1:68">
@@ -27904,7 +27907,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7727627</v>
+        <v>7727635</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -27919,10 +27922,10 @@
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H131" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -27934,175 +27937,175 @@
         <v>1</v>
       </c>
       <c r="L131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131">
         <v>2</v>
       </c>
       <c r="N131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O131" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="P131" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q131">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R131">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S131">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T131">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U131">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="V131">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="W131">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="X131">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y131">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z131">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA131">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB131">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC131">
         <v>1.01</v>
       </c>
       <c r="AD131">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE131">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF131">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="AG131">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AH131">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AI131">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ131">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AK131">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AL131">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AM131">
         <v>1.1</v>
       </c>
       <c r="AN131">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO131">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AP131">
-        <v>0.91</v>
+        <v>1.45</v>
       </c>
       <c r="AQ131">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AR131">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS131">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AT131">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="AU131">
+        <v>-1</v>
+      </c>
+      <c r="AV131">
+        <v>-1</v>
+      </c>
+      <c r="AW131">
+        <v>-1</v>
+      </c>
+      <c r="AX131">
+        <v>-1</v>
+      </c>
+      <c r="AY131">
+        <v>-1</v>
+      </c>
+      <c r="AZ131">
+        <v>-1</v>
+      </c>
+      <c r="BA131">
+        <v>1</v>
+      </c>
+      <c r="BB131">
         <v>4</v>
       </c>
-      <c r="AV131">
-        <v>4</v>
-      </c>
-      <c r="AW131">
-        <v>2</v>
-      </c>
-      <c r="AX131">
-        <v>2</v>
-      </c>
-      <c r="AY131">
-        <v>6</v>
-      </c>
-      <c r="AZ131">
-        <v>6</v>
-      </c>
-      <c r="BA131">
-        <v>4</v>
-      </c>
-      <c r="BB131">
-        <v>9</v>
-      </c>
       <c r="BC131">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BD131">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="BE131">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF131">
+        <v>1.17</v>
+      </c>
+      <c r="BG131">
+        <v>1.25</v>
+      </c>
+      <c r="BH131">
+        <v>3.28</v>
+      </c>
+      <c r="BI131">
         <v>1.48</v>
       </c>
-      <c r="BG131">
-        <v>1.18</v>
-      </c>
-      <c r="BH131">
-        <v>3.84</v>
-      </c>
-      <c r="BI131">
-        <v>1.37</v>
-      </c>
       <c r="BJ131">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="BK131">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BL131">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BM131">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="BN131">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="BO131">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="BP131">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="132" spans="1:68">
@@ -28110,7 +28113,7 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>7727626</v>
+        <v>7727625</v>
       </c>
       <c r="C132" t="s">
         <v>68</v>
@@ -28119,16 +28122,16 @@
         <v>69</v>
       </c>
       <c r="E132" s="2">
-        <v>45674.69791666666</v>
+        <v>45671.69791666666</v>
       </c>
       <c r="F132">
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H132" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -28140,174 +28143,380 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O132" t="s">
+        <v>178</v>
+      </c>
+      <c r="P132" t="s">
         <v>85</v>
       </c>
-      <c r="P132" t="s">
-        <v>246</v>
-      </c>
       <c r="Q132">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S132">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T132">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="U132">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V132">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="W132">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="X132">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y132">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z132">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA132">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB132">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AC132">
         <v>1.01</v>
       </c>
       <c r="AD132">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE132">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>3.34</v>
+        <v>4.75</v>
       </c>
       <c r="AG132">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AH132">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="AI132">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ132">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AK132">
         <v>1.31</v>
       </c>
       <c r="AL132">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AM132">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AN132">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO132">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AP132">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AQ132">
-        <v>1.36</v>
+        <v>0.64</v>
       </c>
       <c r="AR132">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AS132">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AT132">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="AU132">
+        <v>12</v>
+      </c>
+      <c r="AV132">
         <v>4</v>
       </c>
-      <c r="AV132">
-        <v>8</v>
-      </c>
       <c r="AW132">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX132">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY132">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AZ132">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB132">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC132">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD132">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="BE132">
         <v>8.6</v>
       </c>
       <c r="BF132">
+        <v>2.62</v>
+      </c>
+      <c r="BG132">
+        <v>1.2</v>
+      </c>
+      <c r="BH132">
+        <v>4.2</v>
+      </c>
+      <c r="BI132">
+        <v>1.32</v>
+      </c>
+      <c r="BJ132">
+        <v>2.88</v>
+      </c>
+      <c r="BK132">
+        <v>1.57</v>
+      </c>
+      <c r="BL132">
+        <v>2.14</v>
+      </c>
+      <c r="BM132">
+        <v>1.95</v>
+      </c>
+      <c r="BN132">
+        <v>1.77</v>
+      </c>
+      <c r="BO132">
+        <v>2.56</v>
+      </c>
+      <c r="BP132">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7727626</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45674.69791666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>73</v>
+      </c>
+      <c r="H133" t="s">
+        <v>77</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>2</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>85</v>
+      </c>
+      <c r="P133" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q133">
+        <v>2.75</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>3.6</v>
+      </c>
+      <c r="T133">
+        <v>1.4</v>
+      </c>
+      <c r="U133">
+        <v>2.75</v>
+      </c>
+      <c r="V133">
+        <v>2.75</v>
+      </c>
+      <c r="W133">
+        <v>1.4</v>
+      </c>
+      <c r="X133">
+        <v>7</v>
+      </c>
+      <c r="Y133">
+        <v>1.08</v>
+      </c>
+      <c r="Z133">
+        <v>2.02</v>
+      </c>
+      <c r="AA133">
+        <v>3.4</v>
+      </c>
+      <c r="AB133">
+        <v>3.6</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>9</v>
+      </c>
+      <c r="AE133">
+        <v>1.24</v>
+      </c>
+      <c r="AF133">
+        <v>3.34</v>
+      </c>
+      <c r="AG133">
+        <v>1.95</v>
+      </c>
+      <c r="AH133">
+        <v>1.82</v>
+      </c>
+      <c r="AI133">
+        <v>1.73</v>
+      </c>
+      <c r="AJ133">
+        <v>2</v>
+      </c>
+      <c r="AK133">
+        <v>1.31</v>
+      </c>
+      <c r="AL133">
+        <v>1.28</v>
+      </c>
+      <c r="AM133">
+        <v>1.59</v>
+      </c>
+      <c r="AN133">
+        <v>1.4</v>
+      </c>
+      <c r="AO133">
+        <v>1.2</v>
+      </c>
+      <c r="AP133">
+        <v>1.27</v>
+      </c>
+      <c r="AQ133">
+        <v>1.36</v>
+      </c>
+      <c r="AR133">
+        <v>1.54</v>
+      </c>
+      <c r="AS133">
+        <v>1.37</v>
+      </c>
+      <c r="AT133">
+        <v>2.91</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>8</v>
+      </c>
+      <c r="AW133">
+        <v>10</v>
+      </c>
+      <c r="AX133">
+        <v>3</v>
+      </c>
+      <c r="AY133">
+        <v>14</v>
+      </c>
+      <c r="AZ133">
+        <v>11</v>
+      </c>
+      <c r="BA133">
+        <v>4</v>
+      </c>
+      <c r="BB133">
+        <v>6</v>
+      </c>
+      <c r="BC133">
+        <v>10</v>
+      </c>
+      <c r="BD133">
+        <v>1.5</v>
+      </c>
+      <c r="BE133">
+        <v>8.6</v>
+      </c>
+      <c r="BF133">
         <v>2.99</v>
       </c>
-      <c r="BG132">
+      <c r="BG133">
         <v>1.23</v>
       </c>
-      <c r="BH132">
+      <c r="BH133">
         <v>3.42</v>
       </c>
-      <c r="BI132">
+      <c r="BI133">
         <v>1.45</v>
       </c>
-      <c r="BJ132">
+      <c r="BJ133">
         <v>2.41</v>
       </c>
-      <c r="BK132">
+      <c r="BK133">
         <v>1.77</v>
       </c>
-      <c r="BL132">
+      <c r="BL133">
         <v>1.95</v>
       </c>
-      <c r="BM132">
+      <c r="BM133">
         <v>2.3</v>
       </c>
-      <c r="BN132">
+      <c r="BN133">
         <v>1.49</v>
       </c>
-      <c r="BO132">
+      <c r="BO133">
         <v>3.08</v>
       </c>
-      <c r="BP132">
+      <c r="BP133">
         <v>1.28</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="253">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,12 @@
     <t>['47', '80', '84']</t>
   </si>
   <si>
+    <t>['63', '90+4']</t>
+  </si>
+  <si>
+    <t>['19', '23']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -758,6 +764,15 @@
   </si>
   <si>
     <t>['59', '65']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['45+1', '69']</t>
+  </si>
+  <si>
+    <t>['49', '71']</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1375,7 +1390,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1453,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ2">
         <v>0.27</v>
@@ -1581,7 +1596,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1787,7 +1802,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2199,7 +2214,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2280,7 +2295,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ6">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2405,7 +2420,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2689,10 +2704,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ8">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3104,7 +3119,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ10">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3229,7 +3244,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3307,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ11">
         <v>1.09</v>
@@ -3435,7 +3450,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3847,7 +3862,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4134,7 +4149,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4259,7 +4274,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4337,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ16">
         <v>1.91</v>
@@ -4543,10 +4558,10 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ17">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
         <v>0.68</v>
@@ -4671,7 +4686,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4877,7 +4892,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5161,7 +5176,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ20">
         <v>1.82</v>
@@ -5907,7 +5922,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6113,7 +6128,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6194,7 +6209,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ25">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR25">
         <v>1.81</v>
@@ -6319,7 +6334,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6525,7 +6540,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7221,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ30">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR30">
         <v>1.93</v>
@@ -7349,7 +7364,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7555,7 +7570,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7636,7 +7651,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR32">
         <v>1.41</v>
@@ -7967,7 +7982,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8045,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ34">
         <v>0.64</v>
@@ -8251,7 +8266,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35">
         <v>1.45</v>
@@ -8872,7 +8887,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ38">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR38">
         <v>3.26</v>
@@ -8997,7 +9012,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9078,7 +9093,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ39">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>1.1</v>
@@ -9284,7 +9299,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ40">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9409,7 +9424,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9615,7 +9630,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9821,7 +9836,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9899,7 +9914,7 @@
         <v>1.75</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ43">
         <v>1.82</v>
@@ -10105,7 +10120,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ44">
         <v>1.09</v>
@@ -10439,7 +10454,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10645,7 +10660,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10851,7 +10866,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -10932,7 +10947,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ48">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR48">
         <v>1.21</v>
@@ -11138,7 +11153,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ49">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>2.19</v>
@@ -11263,7 +11278,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11469,7 +11484,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11547,7 +11562,7 @@
         <v>2.4</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ51">
         <v>1.45</v>
@@ -11675,7 +11690,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12087,7 +12102,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12165,7 +12180,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ54">
         <v>2.18</v>
@@ -12499,7 +12514,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12705,7 +12720,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12786,7 +12801,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13198,7 +13213,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ59">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>2.07</v>
@@ -13323,7 +13338,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13401,7 +13416,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ60">
         <v>0.64</v>
@@ -13529,7 +13544,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13941,7 +13956,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14019,7 +14034,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ63">
         <v>1.91</v>
@@ -14147,7 +14162,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14559,7 +14574,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15052,7 +15067,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ68">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR68">
         <v>1.7</v>
@@ -15177,7 +15192,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15383,7 +15398,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15461,10 +15476,10 @@
         <v>2.6</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ70">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR70">
         <v>0.96</v>
@@ -15795,7 +15810,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16001,7 +16016,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16285,10 +16300,10 @@
         <v>2.67</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ74">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR74">
         <v>1.22</v>
@@ -16413,7 +16428,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16491,10 +16506,10 @@
         <v>0.83</v>
       </c>
       <c r="AP75">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR75">
         <v>1.8</v>
@@ -16825,7 +16840,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16903,7 +16918,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ77">
         <v>0.82</v>
@@ -17031,7 +17046,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17112,7 +17127,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17237,7 +17252,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17649,7 +17664,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17727,7 +17742,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ81">
         <v>2.18</v>
@@ -17855,7 +17870,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -17936,7 +17951,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ82">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR82">
         <v>1.39</v>
@@ -18061,7 +18076,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18267,7 +18282,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18473,7 +18488,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18554,7 +18569,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -19169,7 +19184,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ88">
         <v>1.36</v>
@@ -19503,7 +19518,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19581,7 +19596,7 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ90">
         <v>0.82</v>
@@ -19915,7 +19930,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20327,7 +20342,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20405,7 +20420,7 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ94">
         <v>1.36</v>
@@ -20739,7 +20754,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21023,7 +21038,7 @@
         <v>0.38</v>
       </c>
       <c r="AP97">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ97">
         <v>0.27</v>
@@ -21232,7 +21247,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ98">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR98">
         <v>1.69</v>
@@ -21563,7 +21578,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21644,7 +21659,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ100">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR100">
         <v>2.55</v>
@@ -21769,7 +21784,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21847,7 +21862,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101">
         <v>1.09</v>
@@ -21975,7 +21990,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22181,7 +22196,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23005,7 +23020,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23289,7 +23304,7 @@
         <v>0.88</v>
       </c>
       <c r="AP108">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ108">
         <v>0.64</v>
@@ -23417,7 +23432,7 @@
         <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23498,7 +23513,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR109">
         <v>1.33</v>
@@ -23623,7 +23638,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23704,7 +23719,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ110">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR110">
         <v>1.27</v>
@@ -23907,7 +23922,7 @@
         <v>2</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ111">
         <v>1.91</v>
@@ -24035,7 +24050,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24116,7 +24131,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ112">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR112">
         <v>2.55</v>
@@ -24241,7 +24256,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24322,7 +24337,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ113">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24447,7 +24462,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24525,10 +24540,10 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ114">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR114">
         <v>1.45</v>
@@ -24653,7 +24668,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q115">
         <v>6</v>
@@ -24937,7 +24952,7 @@
         <v>1.22</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ116">
         <v>1.36</v>
@@ -25065,7 +25080,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25271,7 +25286,7 @@
         <v>85</v>
       </c>
       <c r="P118" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q118">
         <v>3.75</v>
@@ -25349,7 +25364,7 @@
         <v>1.78</v>
       </c>
       <c r="AP118">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ118">
         <v>1.82</v>
@@ -25558,7 +25573,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ119">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR119">
         <v>1.37</v>
@@ -25889,7 +25904,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26588,7 +26603,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.41</v>
@@ -26919,7 +26934,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q126">
         <v>1.44</v>
@@ -27125,7 +27140,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27331,7 +27346,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27409,10 +27424,10 @@
         <v>0.6</v>
       </c>
       <c r="AP128">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ128">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR128">
         <v>1.06</v>
@@ -27743,7 +27758,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q130">
         <v>7</v>
@@ -27821,10 +27836,10 @@
         <v>2.3</v>
       </c>
       <c r="AP130">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ130">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR130">
         <v>1.63</v>
@@ -27949,7 +27964,7 @@
         <v>85</v>
       </c>
       <c r="P131" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q131">
         <v>5.5</v>
@@ -28027,7 +28042,7 @@
         <v>2.1</v>
       </c>
       <c r="AP131">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ131">
         <v>2.18</v>
@@ -28361,7 +28376,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28518,6 +28533,624 @@
       </c>
       <c r="BP133">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7817170</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>75</v>
+      </c>
+      <c r="H134" t="s">
+        <v>76</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>2</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
+      <c r="O134" t="s">
+        <v>179</v>
+      </c>
+      <c r="P134" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q134">
+        <v>4.75</v>
+      </c>
+      <c r="R134">
+        <v>2.3</v>
+      </c>
+      <c r="S134">
+        <v>2.2</v>
+      </c>
+      <c r="T134">
+        <v>1.33</v>
+      </c>
+      <c r="U134">
+        <v>3.25</v>
+      </c>
+      <c r="V134">
+        <v>2.63</v>
+      </c>
+      <c r="W134">
+        <v>1.44</v>
+      </c>
+      <c r="X134">
+        <v>6</v>
+      </c>
+      <c r="Y134">
+        <v>1.11</v>
+      </c>
+      <c r="Z134">
+        <v>4.1</v>
+      </c>
+      <c r="AA134">
+        <v>4.6</v>
+      </c>
+      <c r="AB134">
+        <v>1.64</v>
+      </c>
+      <c r="AC134">
+        <v>1.03</v>
+      </c>
+      <c r="AD134">
+        <v>12.3</v>
+      </c>
+      <c r="AE134">
+        <v>1.22</v>
+      </c>
+      <c r="AF134">
+        <v>3.8</v>
+      </c>
+      <c r="AG134">
+        <v>1.82</v>
+      </c>
+      <c r="AH134">
+        <v>1.92</v>
+      </c>
+      <c r="AI134">
+        <v>1.8</v>
+      </c>
+      <c r="AJ134">
+        <v>1.91</v>
+      </c>
+      <c r="AK134">
+        <v>1.99</v>
+      </c>
+      <c r="AL134">
+        <v>1.18</v>
+      </c>
+      <c r="AM134">
+        <v>1.2</v>
+      </c>
+      <c r="AN134">
+        <v>1.45</v>
+      </c>
+      <c r="AO134">
+        <v>2.36</v>
+      </c>
+      <c r="AP134">
+        <v>1.58</v>
+      </c>
+      <c r="AQ134">
+        <v>2.17</v>
+      </c>
+      <c r="AR134">
+        <v>1.5</v>
+      </c>
+      <c r="AS134">
+        <v>1.61</v>
+      </c>
+      <c r="AT134">
+        <v>3.11</v>
+      </c>
+      <c r="AU134">
+        <v>4</v>
+      </c>
+      <c r="AV134">
+        <v>4</v>
+      </c>
+      <c r="AW134">
+        <v>7</v>
+      </c>
+      <c r="AX134">
+        <v>3</v>
+      </c>
+      <c r="AY134">
+        <v>11</v>
+      </c>
+      <c r="AZ134">
+        <v>7</v>
+      </c>
+      <c r="BA134">
+        <v>8</v>
+      </c>
+      <c r="BB134">
+        <v>7</v>
+      </c>
+      <c r="BC134">
+        <v>15</v>
+      </c>
+      <c r="BD134">
+        <v>3.22</v>
+      </c>
+      <c r="BE134">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF134">
+        <v>1.44</v>
+      </c>
+      <c r="BG134">
+        <v>1.28</v>
+      </c>
+      <c r="BH134">
+        <v>3.08</v>
+      </c>
+      <c r="BI134">
+        <v>1.52</v>
+      </c>
+      <c r="BJ134">
+        <v>2.24</v>
+      </c>
+      <c r="BK134">
+        <v>1.92</v>
+      </c>
+      <c r="BL134">
+        <v>1.75</v>
+      </c>
+      <c r="BM134">
+        <v>2.49</v>
+      </c>
+      <c r="BN134">
+        <v>1.42</v>
+      </c>
+      <c r="BO134">
+        <v>3.42</v>
+      </c>
+      <c r="BP134">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7817171</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>74</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135">
+        <v>2</v>
+      </c>
+      <c r="M135">
+        <v>2</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>180</v>
+      </c>
+      <c r="P135" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q135">
+        <v>2.5</v>
+      </c>
+      <c r="R135">
+        <v>2.5</v>
+      </c>
+      <c r="S135">
+        <v>3.4</v>
+      </c>
+      <c r="T135">
+        <v>1.25</v>
+      </c>
+      <c r="U135">
+        <v>3.75</v>
+      </c>
+      <c r="V135">
+        <v>2.1</v>
+      </c>
+      <c r="W135">
+        <v>1.67</v>
+      </c>
+      <c r="X135">
+        <v>4.5</v>
+      </c>
+      <c r="Y135">
+        <v>1.17</v>
+      </c>
+      <c r="Z135">
+        <v>1.75</v>
+      </c>
+      <c r="AA135">
+        <v>3.85</v>
+      </c>
+      <c r="AB135">
+        <v>3.65</v>
+      </c>
+      <c r="AC135">
+        <v>1.01</v>
+      </c>
+      <c r="AD135">
+        <v>13</v>
+      </c>
+      <c r="AE135">
+        <v>1.13</v>
+      </c>
+      <c r="AF135">
+        <v>5</v>
+      </c>
+      <c r="AG135">
+        <v>1.43</v>
+      </c>
+      <c r="AH135">
+        <v>2.62</v>
+      </c>
+      <c r="AI135">
+        <v>1.44</v>
+      </c>
+      <c r="AJ135">
+        <v>2.63</v>
+      </c>
+      <c r="AK135">
+        <v>1.34</v>
+      </c>
+      <c r="AL135">
+        <v>1.22</v>
+      </c>
+      <c r="AM135">
+        <v>1.64</v>
+      </c>
+      <c r="AN135">
+        <v>0.91</v>
+      </c>
+      <c r="AO135">
+        <v>0.82</v>
+      </c>
+      <c r="AP135">
+        <v>0.92</v>
+      </c>
+      <c r="AQ135">
+        <v>0.83</v>
+      </c>
+      <c r="AR135">
+        <v>1.57</v>
+      </c>
+      <c r="AS135">
+        <v>1.38</v>
+      </c>
+      <c r="AT135">
+        <v>2.95</v>
+      </c>
+      <c r="AU135">
+        <v>6</v>
+      </c>
+      <c r="AV135">
+        <v>7</v>
+      </c>
+      <c r="AW135">
+        <v>6</v>
+      </c>
+      <c r="AX135">
+        <v>7</v>
+      </c>
+      <c r="AY135">
+        <v>12</v>
+      </c>
+      <c r="AZ135">
+        <v>14</v>
+      </c>
+      <c r="BA135">
+        <v>5</v>
+      </c>
+      <c r="BB135">
+        <v>7</v>
+      </c>
+      <c r="BC135">
+        <v>12</v>
+      </c>
+      <c r="BD135">
+        <v>1.62</v>
+      </c>
+      <c r="BE135">
+        <v>7.4</v>
+      </c>
+      <c r="BF135">
+        <v>2.88</v>
+      </c>
+      <c r="BG135">
+        <v>1.22</v>
+      </c>
+      <c r="BH135">
+        <v>3.8</v>
+      </c>
+      <c r="BI135">
+        <v>1.32</v>
+      </c>
+      <c r="BJ135">
+        <v>3.1</v>
+      </c>
+      <c r="BK135">
+        <v>1.63</v>
+      </c>
+      <c r="BL135">
+        <v>2.16</v>
+      </c>
+      <c r="BM135">
+        <v>2.03</v>
+      </c>
+      <c r="BN135">
+        <v>1.72</v>
+      </c>
+      <c r="BO135">
+        <v>2.6</v>
+      </c>
+      <c r="BP135">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7817172</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45681.70833333334</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>78</v>
+      </c>
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>2</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136" t="s">
+        <v>120</v>
+      </c>
+      <c r="P136" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q136">
+        <v>3.75</v>
+      </c>
+      <c r="R136">
+        <v>2.5</v>
+      </c>
+      <c r="S136">
+        <v>2.25</v>
+      </c>
+      <c r="T136">
+        <v>1.25</v>
+      </c>
+      <c r="U136">
+        <v>3.75</v>
+      </c>
+      <c r="V136">
+        <v>2.1</v>
+      </c>
+      <c r="W136">
+        <v>1.67</v>
+      </c>
+      <c r="X136">
+        <v>4.5</v>
+      </c>
+      <c r="Y136">
+        <v>1.17</v>
+      </c>
+      <c r="Z136">
+        <v>3.61</v>
+      </c>
+      <c r="AA136">
+        <v>4.5</v>
+      </c>
+      <c r="AB136">
+        <v>1.76</v>
+      </c>
+      <c r="AC136">
+        <v>1.01</v>
+      </c>
+      <c r="AD136">
+        <v>15.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.13</v>
+      </c>
+      <c r="AF136">
+        <v>5.1</v>
+      </c>
+      <c r="AG136">
+        <v>1.67</v>
+      </c>
+      <c r="AH136">
+        <v>2.1</v>
+      </c>
+      <c r="AI136">
+        <v>1.5</v>
+      </c>
+      <c r="AJ136">
+        <v>2.5</v>
+      </c>
+      <c r="AK136">
+        <v>1.85</v>
+      </c>
+      <c r="AL136">
+        <v>1.19</v>
+      </c>
+      <c r="AM136">
+        <v>1.25</v>
+      </c>
+      <c r="AN136">
+        <v>1</v>
+      </c>
+      <c r="AO136">
+        <v>1.09</v>
+      </c>
+      <c r="AP136">
+        <v>0.92</v>
+      </c>
+      <c r="AQ136">
+        <v>1.25</v>
+      </c>
+      <c r="AR136">
+        <v>1.08</v>
+      </c>
+      <c r="AS136">
+        <v>1.46</v>
+      </c>
+      <c r="AT136">
+        <v>2.54</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>5</v>
+      </c>
+      <c r="AW136">
+        <v>3</v>
+      </c>
+      <c r="AX136">
+        <v>6</v>
+      </c>
+      <c r="AY136">
+        <v>9</v>
+      </c>
+      <c r="AZ136">
+        <v>11</v>
+      </c>
+      <c r="BA136">
+        <v>2</v>
+      </c>
+      <c r="BB136">
+        <v>1</v>
+      </c>
+      <c r="BC136">
+        <v>3</v>
+      </c>
+      <c r="BD136">
+        <v>0</v>
+      </c>
+      <c r="BE136">
+        <v>0</v>
+      </c>
+      <c r="BF136">
+        <v>0</v>
+      </c>
+      <c r="BG136">
+        <v>0</v>
+      </c>
+      <c r="BH136">
+        <v>0</v>
+      </c>
+      <c r="BI136">
+        <v>0</v>
+      </c>
+      <c r="BJ136">
+        <v>0</v>
+      </c>
+      <c r="BK136">
+        <v>0</v>
+      </c>
+      <c r="BL136">
+        <v>0</v>
+      </c>
+      <c r="BM136">
+        <v>0</v>
+      </c>
+      <c r="BN136">
+        <v>0</v>
+      </c>
+      <c r="BO136">
+        <v>0</v>
+      </c>
+      <c r="BP136">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
